--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T08:49:22+00:00</t>
+    <t>2026-03-04T09:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T09:38:55+00:00</t>
+    <t>2026-03-04T10:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Observation sur l’aménagement du moyen de transport</t>
+  </si>
+  <si>
+    <t>REPAS</t>
+  </si>
+  <si>
+    <t>Repas</t>
   </si>
 </sst>
 </file>
@@ -460,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -501,6 +507,18 @@
       </c>
       <c r="D3" s="2"/>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T10:43:17+00:00</t>
+    <t>2026-03-04T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:55:47+00:00</t>
+    <t>2026-03-05T13:54:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:54:22+00:00</t>
+    <t>2026-03-05T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T14:12:55+00:00</t>
+    <t>2026-03-05T15:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:01:37+00:00</t>
+    <t>2026-03-05T15:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:27:35+00:00</t>
+    <t>2026-03-05T16:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T16:09:12+00:00</t>
+    <t>2026-03-06T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T08:12:50+00:00</t>
+    <t>2026-03-09T13:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:07:52+00:00</t>
+    <t>2026-03-17T10:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T10:53:05+00:00</t>
+    <t>2026-06-03T14:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:26:22+00:00</t>
+    <t>2026-06-09T13:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:39+00:00</t>
+    <t>2026-06-11T13:38:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:38:26+00:00</t>
+    <t>2026-06-12T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:33:45+00:00</t>
+    <t>2026-06-12T07:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:50:14+00:00</t>
+    <t>2026-06-12T13:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:52:17+00:00</t>
+    <t>2026-06-15T09:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T09:04:15+00:00</t>
+    <t>2026-06-16T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:03:26+00:00</t>
+    <t>2026-06-16T13:10:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:10:49+00:00</t>
+    <t>2026-06-22T08:40:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:40:39+00:00</t>
+    <t>2026-06-24T07:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
